--- a/AAII_Financials/Quarterly/CMRC_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/CMRC_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="139" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="143" uniqueCount="92">
   <si>
     <t>CMRC</t>
   </si>
@@ -656,186 +656,199 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A5:N102"/>
+  <dimension ref="A5:O102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:15" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:15" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E7" s="2">
         <v>46112</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>46022</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45930</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45838</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45747</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45657</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45565</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45473</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>45382</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>45291</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>45199</v>
       </c>
     </row>
-    <row r="8" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:15" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>84500</v>
+      </c>
+      <c r="E8" s="3">
         <v>86800</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>89500</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>86000</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>84400</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>82400</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>87000</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>83700</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>81800</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>80400</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>84100</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>78000</v>
       </c>
     </row>
-    <row r="9" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:15" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>21000</v>
+      </c>
+      <c r="E9" s="3">
         <v>20200</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>19400</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>18600</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>17700</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>17000</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>19500</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>19900</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>19800</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>18400</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>18900</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>19100</v>
       </c>
     </row>
-    <row r="10" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:15" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>63500</v>
+      </c>
+      <c r="E10" s="3">
         <v>66700</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>70100</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>67400</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>66700</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>65400</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>67600</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>63800</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>62000</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>61900</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>65200</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>59000</v>
       </c>
     </row>
-    <row r="11" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:15" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -850,46 +863,50 @@
       <c r="L11" s="3"/>
       <c r="M11" s="3"/>
       <c r="N11" s="3"/>
-    </row>
-    <row r="12" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O11" s="3"/>
+    </row>
+    <row r="12" spans="1:15" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
       <c r="D12" s="3">
-        <v>18000</v>
+        <v>17700</v>
       </c>
       <c r="E12" s="3">
         <v>18000</v>
       </c>
       <c r="F12" s="3">
+        <v>18000</v>
+      </c>
+      <c r="G12" s="3">
         <v>17500</v>
       </c>
-      <c r="G12" s="3">
+      <c r="H12" s="3">
         <v>18300</v>
       </c>
-      <c r="H12" s="3">
+      <c r="I12" s="3">
         <v>19200</v>
       </c>
-      <c r="I12" s="3">
+      <c r="J12" s="3">
         <v>19800</v>
       </c>
-      <c r="J12" s="3">
+      <c r="K12" s="3">
         <v>20800</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>20300</v>
       </c>
-      <c r="L12" s="3">
+      <c r="M12" s="3">
         <v>20000</v>
       </c>
-      <c r="M12" s="3">
+      <c r="N12" s="3">
         <v>19500</v>
       </c>
-      <c r="N12" s="3">
+      <c r="O12" s="3">
         <v>21700</v>
       </c>
     </row>
-    <row r="13" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:15" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>8</v>
       </c>
@@ -926,46 +943,52 @@
       <c r="N13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:15" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>9</v>
       </c>
       <c r="D14" s="3">
+        <v>0</v>
+      </c>
+      <c r="E14" s="3">
         <v>900</v>
       </c>
-      <c r="E14" s="3">
+      <c r="F14" s="3">
         <v>7400</v>
       </c>
-      <c r="F14" s="3">
+      <c r="G14" s="3">
         <v>100</v>
       </c>
-      <c r="G14" s="3">
+      <c r="H14" s="3">
         <v>1700</v>
       </c>
-      <c r="H14" s="3">
+      <c r="I14" s="3">
         <v>-1700</v>
       </c>
-      <c r="I14" s="3">
+      <c r="J14" s="3">
         <v>1600</v>
       </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>-1900</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>2900</v>
       </c>
-      <c r="L14" s="3">
+      <c r="M14" s="3">
         <v>300</v>
       </c>
-      <c r="M14" s="3">
+      <c r="N14" s="3">
         <v>1200</v>
       </c>
-      <c r="N14" s="3">
+      <c r="O14" s="3">
         <v>6900</v>
       </c>
     </row>
-    <row r="15" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:15" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>10</v>
       </c>
@@ -973,37 +996,40 @@
         <v>1500</v>
       </c>
       <c r="E15" s="3">
+        <v>1500</v>
+      </c>
+      <c r="F15" s="3">
         <v>1700</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>1900</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>2500</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>2300</v>
-      </c>
-      <c r="I15" s="3">
-        <v>2400</v>
       </c>
       <c r="J15" s="3">
         <v>2400</v>
       </c>
       <c r="K15" s="3">
-        <v>2500</v>
+        <v>2400</v>
       </c>
       <c r="L15" s="3">
         <v>2500</v>
       </c>
       <c r="M15" s="3">
+        <v>2500</v>
+      </c>
+      <c r="N15" s="3">
         <v>2300</v>
       </c>
-      <c r="N15" s="3">
+      <c r="O15" s="3">
         <v>2000</v>
       </c>
     </row>
-    <row r="16" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:15" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1015,84 +1041,91 @@
       <c r="L16" s="3"/>
       <c r="M16" s="3"/>
       <c r="N16" s="3"/>
-    </row>
-    <row r="17" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O16" s="3"/>
+    </row>
+    <row r="17" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D17" s="3">
+        <v>81800</v>
+      </c>
+      <c r="E17" s="3">
         <v>80200</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>88700</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>86400</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>89500</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>82500</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>86200</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>92700</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>92400</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>88300</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>88700</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>93400</v>
       </c>
     </row>
-    <row r="18" spans="3:14" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D18" s="3">
+        <v>2700</v>
+      </c>
+      <c r="E18" s="3">
         <v>6700</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>800</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>-400</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>-5100</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>-200</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>800</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>-9000</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>-10600</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>-7900</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>-4500</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>-15300</v>
       </c>
     </row>
-    <row r="19" spans="3:14" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>13</v>
       </c>
@@ -1107,84 +1140,91 @@
       <c r="L19" s="3"/>
       <c r="M19" s="3"/>
       <c r="N19" s="3"/>
-    </row>
-    <row r="20" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O19" s="3"/>
+    </row>
+    <row r="20" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>14</v>
       </c>
       <c r="D20" s="3">
+        <v>100</v>
+      </c>
+      <c r="E20" s="3">
         <v>300</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>200</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>300</v>
       </c>
-      <c r="G20" s="3">
-        <v>0</v>
-      </c>
       <c r="H20" s="3">
+        <v>0</v>
+      </c>
+      <c r="I20" s="3">
         <v>100</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>400</v>
-      </c>
-      <c r="J20" s="3">
-        <v>100</v>
       </c>
       <c r="K20" s="3">
         <v>100</v>
       </c>
       <c r="L20" s="3">
+        <v>100</v>
+      </c>
+      <c r="M20" s="3">
         <v>300</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>500</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>300</v>
       </c>
     </row>
-    <row r="21" spans="3:14" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D21" s="3">
+        <v>4000</v>
+      </c>
+      <c r="E21" s="3">
         <v>7900</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>2300</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>1200</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>-2600</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>2100</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>2800</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>-6700</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>-8200</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>-5800</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>-2700</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>-13600</v>
       </c>
     </row>
-    <row r="22" spans="3:14" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>16</v>
       </c>
@@ -1204,13 +1244,13 @@
         <v>2500</v>
       </c>
       <c r="I22" s="3">
+        <v>2500</v>
+      </c>
+      <c r="J22" s="3">
         <v>2700</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>1900</v>
-      </c>
-      <c r="K22" s="3">
-        <v>700</v>
       </c>
       <c r="L22" s="3">
         <v>700</v>
@@ -1221,54 +1261,60 @@
       <c r="N22" s="3">
         <v>700</v>
       </c>
-    </row>
-    <row r="23" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O22" s="3">
+        <v>700</v>
+      </c>
+    </row>
+    <row r="23" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D23" s="3">
+        <v>1300</v>
+      </c>
+      <c r="E23" s="3">
         <v>4200</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-8200</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-2000</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>-8200</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>200</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>-2100</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>-6700</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-11100</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-6100</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>-3700</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>-20200</v>
       </c>
     </row>
-    <row r="24" spans="3:14" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D24" s="3">
+        <v>200</v>
+      </c>
+      <c r="E24" s="3">
         <v>500</v>
-      </c>
-      <c r="E24" s="3">
-        <v>200</v>
       </c>
       <c r="F24" s="3">
         <v>200</v>
@@ -1277,28 +1323,31 @@
         <v>200</v>
       </c>
       <c r="H24" s="3">
+        <v>200</v>
+      </c>
+      <c r="I24" s="3">
         <v>500</v>
-      </c>
-      <c r="I24" s="3">
-        <v>300</v>
       </c>
       <c r="J24" s="3">
         <v>300</v>
       </c>
       <c r="K24" s="3">
+        <v>300</v>
+      </c>
+      <c r="L24" s="3">
         <v>100</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>300</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>-600</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>100</v>
       </c>
     </row>
-    <row r="25" spans="3:14" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>19</v>
       </c>
@@ -1335,84 +1384,93 @@
       <c r="N25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>20</v>
       </c>
       <c r="D26" s="3">
+        <v>1100</v>
+      </c>
+      <c r="E26" s="3">
         <v>3700</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-8400</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-2200</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>-8400</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>-400</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>-2400</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-7000</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-11300</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-6400</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>-3200</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>-20300</v>
       </c>
     </row>
-    <row r="27" spans="3:14" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D27" s="3">
+        <v>1100</v>
+      </c>
+      <c r="E27" s="3">
         <v>3700</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-8400</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-2200</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>-8400</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>-400</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>-2400</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-7000</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-11300</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-6400</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-3200</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>-20300</v>
       </c>
     </row>
-    <row r="28" spans="3:14" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>22</v>
       </c>
@@ -1449,8 +1507,11 @@
       <c r="N28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>23</v>
       </c>
@@ -1487,8 +1548,11 @@
       <c r="N29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>24</v>
       </c>
@@ -1525,8 +1589,11 @@
       <c r="N30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>25</v>
       </c>
@@ -1563,84 +1630,93 @@
       <c r="N31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>26</v>
       </c>
       <c r="D32" s="3">
+        <v>-100</v>
+      </c>
+      <c r="E32" s="3">
         <v>-300</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>-200</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>-300</v>
       </c>
-      <c r="G32" s="3">
-        <v>0</v>
-      </c>
       <c r="H32" s="3">
+        <v>0</v>
+      </c>
+      <c r="I32" s="3">
         <v>-100</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>-400</v>
-      </c>
-      <c r="J32" s="3">
-        <v>-100</v>
       </c>
       <c r="K32" s="3">
         <v>-100</v>
       </c>
       <c r="L32" s="3">
+        <v>-100</v>
+      </c>
+      <c r="M32" s="3">
         <v>-300</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>-500</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>-300</v>
       </c>
     </row>
-    <row r="33" spans="2:14" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D33" s="3">
+        <v>1100</v>
+      </c>
+      <c r="E33" s="3">
         <v>3700</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-8400</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-2200</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>-8400</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>-400</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>-2400</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>-7000</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-11300</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-6400</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-3200</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>-20300</v>
       </c>
     </row>
-    <row r="34" spans="2:14" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>28</v>
       </c>
@@ -1677,89 +1753,98 @@
       <c r="N34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>29</v>
       </c>
       <c r="D35" s="3">
+        <v>1100</v>
+      </c>
+      <c r="E35" s="3">
         <v>3700</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-8400</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-2200</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>-8400</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>-400</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>-2400</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>-7000</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-11300</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-6400</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-3200</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>-20300</v>
       </c>
     </row>
-    <row r="37" spans="2:14" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:15" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="38" spans="2:14" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E38" s="2">
         <v>46112</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>46022</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45930</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45838</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45747</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45657</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45565</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45473</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>45382</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>45291</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>45199</v>
       </c>
     </row>
-    <row r="39" spans="2:14" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>31</v>
       </c>
@@ -1774,8 +1859,9 @@
       <c r="L39" s="3"/>
       <c r="M39" s="3"/>
       <c r="N39" s="3"/>
-    </row>
-    <row r="40" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O39" s="3"/>
+    </row>
+    <row r="40" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>32</v>
       </c>
@@ -1790,8 +1876,9 @@
       <c r="L40" s="3"/>
       <c r="M40" s="3"/>
       <c r="N40" s="3"/>
-    </row>
-    <row r="41" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O40" s="3"/>
+    </row>
+    <row r="41" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>33</v>
       </c>
@@ -1799,113 +1886,122 @@
         <v>57200</v>
       </c>
       <c r="E41" s="3">
+        <v>57200</v>
+      </c>
+      <c r="F41" s="3">
         <v>44300</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>49900</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>46300</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>52100</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>88900</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>35400</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>133100</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>60900</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>71700</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>69800</v>
       </c>
     </row>
-    <row r="42" spans="2:14" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D42" s="3">
+        <v>99200</v>
+      </c>
+      <c r="E42" s="3">
         <v>97900</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>96800</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>92100</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>88200</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>68600</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>89300</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>133000</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>142700</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>204300</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>198400</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>195600</v>
       </c>
     </row>
-    <row r="43" spans="2:14" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D43" s="3">
+        <v>53400</v>
+      </c>
+      <c r="E43" s="3">
         <v>51800</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>50000</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>51100</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>51800</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>44200</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>48100</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>51200</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>45100</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>39300</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>37700</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>51800</v>
       </c>
     </row>
-    <row r="44" spans="2:14" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>36</v>
       </c>
@@ -1942,84 +2038,93 @@
       <c r="N44" s="3" t="s">
         <v>37</v>
       </c>
-    </row>
-    <row r="45" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O44" s="3" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="45" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>4800</v>
+      </c>
+      <c r="E45" s="3">
         <v>5200</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>6000</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>6800</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>7600</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>8100</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>8800</v>
-      </c>
-      <c r="J45" s="3">
-        <v>9100</v>
       </c>
       <c r="K45" s="3">
         <v>9100</v>
       </c>
       <c r="L45" s="3">
+        <v>9100</v>
+      </c>
+      <c r="M45" s="3">
         <v>8700</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>8300</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>7600</v>
       </c>
     </row>
-    <row r="46" spans="2:14" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>229500</v>
+      </c>
+      <c r="E46" s="3">
         <v>230000</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>214400</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>216000</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>209700</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>192700</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>251200</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>243500</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>355800</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>343500</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>342000</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>341500</v>
       </c>
     </row>
-    <row r="47" spans="2:14" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -2056,84 +2161,93 @@
       <c r="N47" s="3" t="s">
         <v>37</v>
       </c>
-    </row>
-    <row r="48" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O47" s="3" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="48" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>25800</v>
+      </c>
+      <c r="E48" s="3">
         <v>22900</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>21100</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>18700</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>16100</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>15600</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>11100</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>11700</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>13600</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>14000</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>14600</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>15200</v>
       </c>
     </row>
-    <row r="49" spans="3:14" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>60200</v>
+      </c>
+      <c r="E49" s="3">
         <v>61700</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>63200</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>64900</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>66800</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>69400</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>69200</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>71600</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>74100</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>76700</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>79100</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>71200</v>
       </c>
     </row>
-    <row r="50" spans="3:14" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2170,8 +2284,11 @@
       <c r="N50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2208,46 +2325,52 @@
       <c r="N51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>6600</v>
+      </c>
+      <c r="E52" s="3">
         <v>6800</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>4200</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>6200</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>5800</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>4300</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>3100</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>2400</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>2600</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>1800</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>1200</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>600</v>
       </c>
     </row>
-    <row r="53" spans="3:14" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2284,46 +2407,52 @@
       <c r="N53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>324800</v>
+      </c>
+      <c r="E54" s="3">
         <v>324300</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>308800</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>309500</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>302500</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>286300</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>340300</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>335100</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>452500</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>442500</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>444100</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>436000</v>
       </c>
     </row>
-    <row r="55" spans="3:14" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2338,8 +2467,9 @@
       <c r="L55" s="3"/>
       <c r="M55" s="3"/>
       <c r="N55" s="3"/>
-    </row>
-    <row r="56" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O55" s="3"/>
+    </row>
+    <row r="56" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -2354,46 +2484,50 @@
       <c r="L56" s="3"/>
       <c r="M56" s="3"/>
       <c r="N56" s="3"/>
-    </row>
-    <row r="57" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O56" s="3"/>
+    </row>
+    <row r="57" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>9300</v>
+      </c>
+      <c r="E57" s="3">
         <v>8500</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>9900</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>9500</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>8800</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>7800</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>7000</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>8100</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>6700</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>7100</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>8000</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>6300</v>
       </c>
     </row>
-    <row r="58" spans="3:14" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
@@ -2401,189 +2535,204 @@
         <v>5800</v>
       </c>
       <c r="E58" s="3">
+        <v>5800</v>
+      </c>
+      <c r="F58" s="3">
         <v>5600</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>1500</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>1800</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>2000</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>2400</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>3200</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>2800</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>3000</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>2500</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>2900</v>
       </c>
     </row>
-    <row r="59" spans="3:14" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>74600</v>
+      </c>
+      <c r="E59" s="3">
         <v>75700</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>68800</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>63200</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>60700</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>54200</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>53300</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>60900</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>52000</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>44000</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>42600</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>42300</v>
       </c>
     </row>
-    <row r="60" spans="3:14" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>113300</v>
+      </c>
+      <c r="E60" s="3">
         <v>116400</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>108200</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>101000</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>98300</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>82300</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>88000</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>86600</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>78800</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>67900</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>70800</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>67100</v>
       </c>
     </row>
-    <row r="61" spans="3:14" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>158700</v>
+      </c>
+      <c r="E61" s="3">
         <v>159300</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>159900</v>
-      </c>
-      <c r="F61" s="3">
-        <v>164300</v>
       </c>
       <c r="G61" s="3">
         <v>164300</v>
       </c>
       <c r="H61" s="3">
+        <v>164300</v>
+      </c>
+      <c r="I61" s="3">
         <v>164800</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>218100</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>218800</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>346900</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>347000</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>347200</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>347500</v>
       </c>
     </row>
-    <row r="62" spans="3:14" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>1200</v>
+      </c>
+      <c r="E62" s="3">
         <v>1600</v>
-      </c>
-      <c r="E62" s="3">
-        <v>1300</v>
       </c>
       <c r="F62" s="3">
         <v>1300</v>
       </c>
       <c r="G62" s="3">
-        <v>1200</v>
+        <v>1300</v>
       </c>
       <c r="H62" s="3">
         <v>1200</v>
       </c>
       <c r="I62" s="3">
-        <v>800</v>
+        <v>1200</v>
       </c>
       <c r="J62" s="3">
         <v>800</v>
       </c>
       <c r="K62" s="3">
+        <v>800</v>
+      </c>
+      <c r="L62" s="3">
         <v>700</v>
-      </c>
-      <c r="L62" s="3">
-        <v>600</v>
       </c>
       <c r="M62" s="3">
         <v>600</v>
       </c>
       <c r="N62" s="3">
+        <v>600</v>
+      </c>
+      <c r="O62" s="3">
         <v>800</v>
       </c>
     </row>
-    <row r="63" spans="3:14" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -2620,8 +2769,11 @@
       <c r="N63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>19</v>
       </c>
@@ -2658,8 +2810,11 @@
       <c r="N64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -2696,46 +2851,52 @@
       <c r="N65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>273200</v>
+      </c>
+      <c r="E66" s="3">
         <v>277400</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>269400</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>266600</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>263800</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>248200</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>306900</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>306200</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>426400</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>415600</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>418500</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>416100</v>
       </c>
     </row>
-    <row r="67" spans="2:14" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -2750,8 +2911,9 @@
       <c r="L67" s="3"/>
       <c r="M67" s="3"/>
       <c r="N67" s="3"/>
-    </row>
-    <row r="68" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O67" s="3"/>
+    </row>
+    <row r="68" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -2788,8 +2950,11 @@
       <c r="N68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -2826,8 +2991,11 @@
       <c r="N69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -2864,8 +3032,11 @@
       <c r="N70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -2902,46 +3073,52 @@
       <c r="N71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-636200</v>
+      </c>
+      <c r="E72" s="3">
         <v>-637300</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-641000</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-632700</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-630400</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-622000</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-621700</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-619300</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-612300</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-601100</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-594700</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-591500</v>
       </c>
     </row>
-    <row r="73" spans="2:14" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -2978,8 +3155,11 @@
       <c r="N73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -3016,8 +3196,11 @@
       <c r="N74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -3054,46 +3237,52 @@
       <c r="N75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>51600</v>
+      </c>
+      <c r="E76" s="3">
         <v>46900</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>39400</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>42800</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>38800</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>38100</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>33400</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>29000</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>26100</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>26900</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>25500</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>19900</v>
       </c>
     </row>
-    <row r="77" spans="2:14" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -3130,89 +3319,98 @@
       <c r="N77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:15" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:14" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E80" s="2">
         <v>46112</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>46022</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45930</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45838</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45747</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45657</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45565</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45473</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>45382</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>45291</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>45199</v>
       </c>
     </row>
-    <row r="81" spans="3:14" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D81" s="3">
+        <v>1100</v>
+      </c>
+      <c r="E81" s="3">
         <v>3700</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-8400</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-2200</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>-8400</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>-400</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>-2400</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>-7000</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-11300</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-6400</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-3200</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>-20300</v>
       </c>
     </row>
-    <row r="82" spans="3:14" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -3227,46 +3425,50 @@
       <c r="L82" s="3"/>
       <c r="M82" s="3"/>
       <c r="N82" s="3"/>
-    </row>
-    <row r="83" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O82" s="3"/>
+    </row>
+    <row r="83" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>1300</v>
+      </c>
+      <c r="E83" s="3">
         <v>1900</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>900</v>
-      </c>
-      <c r="F83" s="3">
-        <v>1100</v>
       </c>
       <c r="G83" s="3">
         <v>1100</v>
       </c>
       <c r="H83" s="3">
+        <v>1100</v>
+      </c>
+      <c r="I83" s="3">
         <v>1000</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>1200</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>1100</v>
-      </c>
-      <c r="K83" s="3">
-        <v>900</v>
       </c>
       <c r="L83" s="3">
         <v>900</v>
       </c>
       <c r="M83" s="3">
+        <v>900</v>
+      </c>
+      <c r="N83" s="3">
         <v>800</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>1000</v>
       </c>
     </row>
-    <row r="84" spans="3:14" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -3303,8 +3505,11 @@
       <c r="N84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -3341,8 +3546,11 @@
       <c r="N85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -3379,8 +3587,11 @@
       <c r="N86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -3417,8 +3628,11 @@
       <c r="N87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -3455,46 +3669,52 @@
       <c r="N88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>5100</v>
+      </c>
+      <c r="E89" s="3">
         <v>18400</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>1000</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>10600</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>13600</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>400</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>12400</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>5600</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>11700</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>-3400</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>13300</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>-31400</v>
       </c>
     </row>
-    <row r="90" spans="3:14" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -3509,46 +3729,50 @@
       <c r="L90" s="3"/>
       <c r="M90" s="3"/>
       <c r="N90" s="3"/>
-    </row>
-    <row r="91" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O90" s="3"/>
+    </row>
+    <row r="91" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-5000</v>
+      </c>
+      <c r="E91" s="3">
         <v>-4300</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-3200</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-3000</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-1700</v>
-      </c>
-      <c r="H91" s="3">
-        <v>-800</v>
       </c>
       <c r="I91" s="3">
         <v>-800</v>
       </c>
       <c r="J91" s="3">
-        <v>-1100</v>
+        <v>-800</v>
       </c>
       <c r="K91" s="3">
         <v>-1100</v>
       </c>
       <c r="L91" s="3">
+        <v>-1100</v>
+      </c>
+      <c r="M91" s="3">
         <v>-800</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-1000</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-1100</v>
       </c>
     </row>
-    <row r="92" spans="3:14" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -3585,8 +3809,11 @@
       <c r="N92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -3623,46 +3850,52 @@
       <c r="N93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-5700</v>
+      </c>
+      <c r="E94" s="3">
         <v>-5400</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-6000</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-6800</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-21200</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>17400</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>42600</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>9300</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>60300</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-6900</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-11200</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>26400</v>
       </c>
     </row>
-    <row r="95" spans="3:14" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -3677,8 +3910,9 @@
       <c r="L95" s="3"/>
       <c r="M95" s="3"/>
       <c r="N95" s="3"/>
-    </row>
-    <row r="96" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O95" s="3"/>
+    </row>
+    <row r="96" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -3715,8 +3949,11 @@
       <c r="N96" s="3" t="s">
         <v>37</v>
       </c>
-    </row>
-    <row r="97" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O96" s="3" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="97" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -3753,8 +3990,11 @@
       <c r="N97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -3791,8 +4031,11 @@
       <c r="N98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -3829,46 +4072,52 @@
       <c r="N99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-200</v>
+      </c>
+      <c r="E100" s="3">
         <v>-100</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>100</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-100</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>1800</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-54900</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-1600</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-112100</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>100</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-500</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-100</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>300</v>
       </c>
     </row>
-    <row r="101" spans="3:14" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -3905,42 +4154,48 @@
       <c r="N101" s="3" t="s">
         <v>37</v>
       </c>
-    </row>
-    <row r="102" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O101" s="3" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="102" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-800</v>
+      </c>
+      <c r="E102" s="3">
         <v>12900</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-4900</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>3600</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-5800</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-37100</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>53400</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-97300</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>72200</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-10800</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>2000</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-4700</v>
       </c>
     </row>
